--- a/templates/1120S_WTB_Template.xlsx
+++ b/templates/1120S_WTB_Template.xlsx
@@ -35,7 +35,7 @@
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="44">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -281,8 +281,31 @@
       <color rgb="000000FF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00F07840"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00F07840"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -402,8 +425,20 @@
         <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E7"/>
+        <bgColor rgb="00FFF8E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F0F0"/>
+        <bgColor rgb="00F0F0F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -505,6 +540,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00808080"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
@@ -514,7 +568,7 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="5"/>
   </cellStyleXfs>
-  <cellXfs count="200">
+  <cellXfs count="267">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -927,6 +981,167 @@
     <xf numFmtId="164" fontId="36" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="22" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="4" fontId="27" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="28" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="35" fillId="22" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="22" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="9" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="27" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="4" fontId="28" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="35" fillId="22" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="22" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="22" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="22" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="22" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="166" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="166" fontId="0" fillId="22" borderId="10" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="43" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="22" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1644,7 +1859,7 @@
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="143">
-      <c r="A3" s="145" t="inlineStr">
+      <c r="A3" s="261" t="inlineStr">
         <is>
           <t>M-2 is TAX BASIS. PBC Balance Sheet is BOOK BASIS. The equity tie-out at the bottom reconciles the difference.</t>
         </is>
@@ -1731,27 +1946,27 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="143">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="262" t="inlineStr">
         <is>
           <t>2. Ordinary business income (loss)</t>
         </is>
       </c>
-      <c r="B9" s="82">
+      <c r="B9" s="250">
         <f>'Working Trial Balance'!F155</f>
         <v/>
       </c>
       <c r="C9" s="31" t="n"/>
       <c r="D9" s="31" t="n"/>
-      <c r="E9" s="82">
+      <c r="E9" s="250">
         <f>'PBC - P&amp;L2'!B63</f>
         <v/>
       </c>
-      <c r="F9" s="62" t="inlineStr">
+      <c r="F9" s="252" t="inlineStr">
         <is>
           <t>K Ln 1 / Pg 1 Ln 21</t>
         </is>
       </c>
-      <c r="G9" s="63" t="inlineStr">
+      <c r="G9" s="263" t="inlineStr">
         <is>
           <t>AAA = tax OBI from WTB. RE = book net income from P&amp;L.</t>
         </is>
@@ -1875,23 +2090,23 @@
       </c>
     </row>
     <row r="15" ht="41.25" customHeight="1" s="143">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="262" t="inlineStr">
         <is>
           <t>3f. Ordinary gain (§1245 recapture)</t>
         </is>
       </c>
-      <c r="B15" s="186" t="n">
+      <c r="B15" s="264" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="31" t="n"/>
       <c r="D15" s="31" t="n"/>
       <c r="E15" s="31" t="n"/>
-      <c r="F15" s="62" t="inlineStr">
+      <c r="F15" s="252" t="inlineStr">
         <is>
           <t>Pg 1 Ln 4 / F.4797</t>
         </is>
       </c>
-      <c r="G15" s="63" t="inlineStr">
+      <c r="G15" s="263" t="inlineStr">
         <is>
           <t>§1245 recapture ($10K) is ORDINARY income → Pg 1 Ln 4 → Ln 21 → already in OBI (Ln 2 above). DO NOT add here — would double count.</t>
         </is>
@@ -1943,24 +2158,24 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="143">
-      <c r="A18" s="42" t="inlineStr">
+      <c r="A18" s="262" t="inlineStr">
         <is>
           <t>Total Increases</t>
         </is>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="202">
         <f>SUM(B9:B17)</f>
         <v/>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="202">
         <f>SUM(C9:C17)</f>
         <v/>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="202">
         <f>SUM(D9:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="202">
         <f>SUM(E9:E17)</f>
         <v/>
       </c>
@@ -1982,7 +2197,7 @@
       <c r="G20" s="8" t="n"/>
     </row>
     <row r="21" ht="27.75" customHeight="1" s="143">
-      <c r="A21" s="31" t="inlineStr">
+      <c r="A21" s="262" t="inlineStr">
         <is>
           <t>4a. Ordinary business loss</t>
         </is>
@@ -1991,12 +2206,12 @@
       <c r="C21" s="31" t="n"/>
       <c r="D21" s="31" t="n"/>
       <c r="E21" s="31" t="n"/>
-      <c r="F21" s="62" t="inlineStr">
+      <c r="F21" s="252" t="inlineStr">
         <is>
           <t>K Ln 1</t>
         </is>
       </c>
-      <c r="G21" s="63" t="inlineStr">
+      <c r="G21" s="263" t="inlineStr">
         <is>
           <t>If loss year — decreases AAA (can go negative from losses)</t>
         </is>
@@ -2146,41 +2361,41 @@
       </c>
     </row>
     <row r="31" hidden="1" ht="15" customHeight="1" s="143">
-      <c r="A31" s="89" t="inlineStr">
+      <c r="A31" s="265" t="inlineStr">
         <is>
           <t xml:space="preserve">     Total nondeductible $___</t>
         </is>
       </c>
-      <c r="F31" s="91" t="inlineStr">
+      <c r="F31" s="252" t="inlineStr">
         <is>
           <t>K Ln 16c</t>
         </is>
       </c>
-      <c r="G31" s="90" t="inlineStr">
+      <c r="G31" s="263" t="inlineStr">
         <is>
           <t>Reduces SH basis. Does NOT reduce AAA.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="143">
-      <c r="A32" s="42" t="inlineStr">
+      <c r="A32" s="262" t="inlineStr">
         <is>
           <t>Total Decreases</t>
         </is>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="202">
         <f>SUM(B21:B24)</f>
         <v/>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="202">
         <f>SUM(C21:C24)</f>
         <v/>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="202">
         <f>SUM(D21:D24)</f>
         <v/>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="202">
         <f>SUM(E21:E24)</f>
         <v/>
       </c>
@@ -2332,7 +2547,7 @@
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="143">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="261" t="inlineStr">
         <is>
           <t xml:space="preserve">   Distributions</t>
         </is>
@@ -2629,12 +2844,12 @@
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="143">
-      <c r="A70" s="173" t="inlineStr">
+      <c r="A70" s="201" t="inlineStr">
         <is>
           <t xml:space="preserve">   = Total explained differences</t>
         </is>
       </c>
-      <c r="B70" s="32">
+      <c r="B70" s="202">
         <f>SUM(B63:B69)</f>
         <v/>
       </c>
@@ -3812,7 +4027,7 @@
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="143">
-      <c r="A55" s="172" t="inlineStr">
+      <c r="A55" s="266" t="inlineStr">
         <is>
           <t>• If total assets ≤ $250K at EOY, the IRS does not require Sch L (check Box G on page 1). Still recommended as a workpaper.</t>
         </is>
@@ -5045,7 +5260,7 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="143">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="200" t="inlineStr">
         <is>
           <t>INCOME ITEMS</t>
         </is>
@@ -5361,24 +5576,24 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="143">
-      <c r="A18" s="64" t="inlineStr">
+      <c r="A18" s="242" t="inlineStr">
         <is>
           <t>TOTAL INCOME ITEMS</t>
         </is>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="202">
         <f>SUM(B8:B17)</f>
         <v/>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="202">
         <f>SUM(C8:C17)</f>
         <v/>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="202">
         <f>SUM(D8:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="202">
         <f>SUM(E8:E17)</f>
         <v/>
       </c>
@@ -5963,24 +6178,24 @@
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="143">
-      <c r="A40" s="64" t="inlineStr">
+      <c r="A40" s="242" t="inlineStr">
         <is>
           <t>TOTAL EXPENSE ITEMS</t>
         </is>
       </c>
-      <c r="B40" s="32">
+      <c r="B40" s="202">
         <f>SUM(B21:B39)</f>
         <v/>
       </c>
-      <c r="C40" s="32">
+      <c r="C40" s="202">
         <f>SUM(C21:C39)</f>
         <v/>
       </c>
-      <c r="D40" s="32">
+      <c r="D40" s="202">
         <f>SUM(D21:D39)</f>
         <v/>
       </c>
-      <c r="E40" s="32">
+      <c r="E40" s="202">
         <f>SUM(E21:E39)</f>
         <v/>
       </c>
@@ -5988,31 +6203,31 @@
       <c r="G40" s="64" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="143">
-      <c r="A41" s="148" t="inlineStr">
+      <c r="A41" s="259" t="inlineStr">
         <is>
           <t>NET INCOME RECONCILIATION</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="143">
-      <c r="A42" s="65" t="inlineStr">
+      <c r="A42" s="242" t="inlineStr">
         <is>
           <t>Net income (loss) = Income − Expenses</t>
         </is>
       </c>
-      <c r="B42" s="39">
+      <c r="B42" s="245">
         <f>B18-B40</f>
         <v/>
       </c>
-      <c r="C42" s="39">
+      <c r="C42" s="245">
         <f>C18-C40</f>
         <v/>
       </c>
-      <c r="D42" s="39">
+      <c r="D42" s="245">
         <f>D18-D40</f>
         <v/>
       </c>
-      <c r="E42" s="39">
+      <c r="E42" s="245">
         <f>E18-E40</f>
         <v/>
       </c>
@@ -6098,7 +6313,7 @@
       <c r="G51" s="168" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1" s="143">
-      <c r="A52" s="168" t="inlineStr">
+      <c r="A52" s="261" t="inlineStr">
         <is>
           <t xml:space="preserve">   M-1 Line 7 (income per return from WTB)</t>
         </is>
@@ -6321,25 +6536,25 @@
       <c r="G72" s="168" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1" s="143">
-      <c r="A73" s="173" t="inlineStr">
+      <c r="A73" s="201" t="inlineStr">
         <is>
           <t>CHECK 5: Ordinary Business Income tie to WTB / Pg 1, Ln 21 / Sch K, Ln 1</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="143">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="201" t="inlineStr">
         <is>
           <t xml:space="preserve">   WTB Ordinary Business Income</t>
         </is>
       </c>
-      <c r="B74" s="10">
+      <c r="B74" s="250">
         <f>'Working Trial Balance'!D144</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="143">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="261" t="inlineStr">
         <is>
           <t xml:space="preserve">   M-1 Line 1 (net income per books)</t>
         </is>
@@ -10554,7 +10769,7 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="143">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="200" t="inlineStr">
         <is>
           <t>REVENUE</t>
         </is>
@@ -10594,18 +10809,18 @@
       <c r="B10" s="185" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="143">
-      <c r="A11" s="173" t="inlineStr">
+      <c r="A11" s="201" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="202">
         <f>SUM(B7:B10)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="143">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="200" t="inlineStr">
         <is>
           <t>COST OF GOODS SOLD</t>
         </is>
@@ -10637,12 +10852,12 @@
       <c r="B15" s="185" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="143">
-      <c r="A16" s="173" t="inlineStr">
+      <c r="A16" s="201" t="inlineStr">
         <is>
           <t>Total COGS</t>
         </is>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="202">
         <f>SUM(B13:B15)</f>
         <v/>
       </c>
@@ -10659,7 +10874,7 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="143">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="200" t="inlineStr">
         <is>
           <t>OPERATING EXPENSES</t>
         </is>
@@ -10915,12 +11130,12 @@
       <c r="B49" s="185" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1" s="143">
-      <c r="A50" s="173" t="inlineStr">
+      <c r="A50" s="201" t="inlineStr">
         <is>
           <t>Total Operating Expenses</t>
         </is>
       </c>
-      <c r="B50" s="12">
+      <c r="B50" s="202">
         <f>SUM(B19:B49)</f>
         <v/>
       </c>
@@ -10937,7 +11152,7 @@
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="143">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="200" t="inlineStr">
         <is>
           <t>OTHER INCOME / (EXPENSE)</t>
         </is>
@@ -11016,23 +11231,23 @@
       <c r="B61" s="185" t="n"/>
     </row>
     <row r="62" ht="15" customHeight="1" s="143">
-      <c r="A62" s="173" t="inlineStr">
+      <c r="A62" s="201" t="inlineStr">
         <is>
           <t>Total Other Income / (Expense)</t>
         </is>
       </c>
-      <c r="B62" s="12">
+      <c r="B62" s="202">
         <f>SUM(B53:B61)</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="143">
-      <c r="A63" s="173" t="inlineStr">
+      <c r="A63" s="201" t="inlineStr">
         <is>
           <t>NET INCOME PER BOOKS</t>
         </is>
       </c>
-      <c r="B63" s="12">
+      <c r="B63" s="202">
         <f>B51+B62</f>
         <v/>
       </c>
@@ -11706,429 +11921,463 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="187" t="inlineStr">
+      <c r="A1" s="203" t="inlineStr">
         <is>
           <t>PASTE CLIENT BALANCE SHEET FROM QUICKBOOKS HERE</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="188" t="inlineStr">
+      <c r="A2" s="204" t="inlineStr">
         <is>
           <t>Column A = Account Name, Column B = Current Year, Column C = Prior Year</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="188" t="inlineStr">
+      <c r="A3" s="204" t="inlineStr">
         <is>
           <t>Row 88: Total Equity, Row 89: Total L&amp;E (referenced by M-2 formulas)</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="205" t="n"/>
+      <c r="B4" s="205" t="n"/>
+      <c r="C4" s="205" t="n"/>
+    </row>
     <row r="5">
-      <c r="A5" s="154" t="n"/>
-      <c r="B5" s="154" t="n"/>
-      <c r="C5" s="155" t="n"/>
+      <c r="A5" s="206" t="n"/>
+      <c r="B5" s="206" t="n"/>
+      <c r="C5" s="205" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="105" t="n"/>
-      <c r="C6" s="154" t="n"/>
+      <c r="A6" s="205" t="n"/>
+      <c r="B6" s="206" t="n"/>
+      <c r="C6" s="206" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="106" t="n"/>
+      <c r="A7" s="207" t="n"/>
+      <c r="B7" s="205" t="n"/>
+      <c r="C7" s="205" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="107" t="n"/>
+      <c r="A8" s="208" t="n"/>
+      <c r="B8" s="205" t="n"/>
+      <c r="C8" s="205" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="108" t="n"/>
+      <c r="A9" s="209" t="n"/>
+      <c r="B9" s="205" t="n"/>
+      <c r="C9" s="205" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="109" t="n"/>
-      <c r="B10" s="110" t="n"/>
-      <c r="C10" s="110" t="n"/>
+      <c r="A10" s="210" t="n"/>
+      <c r="B10" s="211" t="n"/>
+      <c r="C10" s="211" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="111" t="n"/>
-      <c r="B11" s="112" t="n"/>
-      <c r="C11" s="112" t="n"/>
+      <c r="A11" s="212" t="n"/>
+      <c r="B11" s="213" t="n"/>
+      <c r="C11" s="213" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="111" t="n"/>
-      <c r="B12" s="112" t="n"/>
-      <c r="C12" s="112" t="n"/>
+      <c r="A12" s="212" t="n"/>
+      <c r="B12" s="213" t="n"/>
+      <c r="C12" s="213" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="111" t="n"/>
-      <c r="B13" s="112" t="n"/>
-      <c r="C13" s="112" t="n"/>
+      <c r="A13" s="212" t="n"/>
+      <c r="B13" s="213" t="n"/>
+      <c r="C13" s="213" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="113" t="n"/>
-      <c r="B14" s="114" t="n"/>
-      <c r="C14" s="114" t="n"/>
+      <c r="A14" s="214" t="n"/>
+      <c r="B14" s="215" t="n"/>
+      <c r="C14" s="215" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="109" t="n"/>
-      <c r="B15" s="112" t="n"/>
-      <c r="C15" s="112" t="n"/>
+      <c r="A15" s="210" t="n"/>
+      <c r="B15" s="213" t="n"/>
+      <c r="C15" s="213" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="115" t="n"/>
-      <c r="B16" s="114" t="n"/>
-      <c r="C16" s="114" t="n"/>
+      <c r="A16" s="216" t="n"/>
+      <c r="B16" s="215" t="n"/>
+      <c r="C16" s="215" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="108" t="n"/>
+      <c r="A17" s="209" t="n"/>
+      <c r="B17" s="205" t="n"/>
+      <c r="C17" s="205" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="109" t="n"/>
-      <c r="B18" s="112" t="n"/>
-      <c r="C18" s="112" t="n"/>
+      <c r="A18" s="210" t="n"/>
+      <c r="B18" s="213" t="n"/>
+      <c r="C18" s="213" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="115" t="n"/>
-      <c r="B19" s="114" t="n"/>
-      <c r="C19" s="114" t="n"/>
+      <c r="A19" s="216" t="n"/>
+      <c r="B19" s="215" t="n"/>
+      <c r="C19" s="215" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="108" t="n"/>
+      <c r="A20" s="209" t="n"/>
+      <c r="B20" s="205" t="n"/>
+      <c r="C20" s="205" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="109" t="n"/>
-      <c r="B21" s="110" t="n"/>
-      <c r="C21" s="110" t="n"/>
+      <c r="A21" s="210" t="n"/>
+      <c r="B21" s="211" t="n"/>
+      <c r="C21" s="211" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="111" t="n"/>
-      <c r="B22" s="112" t="n"/>
-      <c r="C22" s="112" t="n"/>
+      <c r="A22" s="212" t="n"/>
+      <c r="B22" s="213" t="n"/>
+      <c r="C22" s="213" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="111" t="n"/>
-      <c r="B23" s="112" t="n"/>
-      <c r="C23" s="112" t="n"/>
+      <c r="A23" s="212" t="n"/>
+      <c r="B23" s="213" t="n"/>
+      <c r="C23" s="213" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="111" t="n"/>
-      <c r="B24" s="112" t="n"/>
-      <c r="C24" s="112" t="n"/>
+      <c r="A24" s="212" t="n"/>
+      <c r="B24" s="213" t="n"/>
+      <c r="C24" s="213" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="111" t="n"/>
-      <c r="B25" s="112" t="n"/>
-      <c r="C25" s="112" t="n"/>
+      <c r="A25" s="212" t="n"/>
+      <c r="B25" s="213" t="n"/>
+      <c r="C25" s="213" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="111" t="n"/>
-      <c r="B26" s="112" t="n"/>
-      <c r="C26" s="112" t="n"/>
+      <c r="A26" s="212" t="n"/>
+      <c r="B26" s="213" t="n"/>
+      <c r="C26" s="213" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="113" t="n"/>
-      <c r="B27" s="114" t="n"/>
-      <c r="C27" s="114" t="n"/>
+      <c r="A27" s="214" t="n"/>
+      <c r="B27" s="215" t="n"/>
+      <c r="C27" s="215" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="109" t="n"/>
-      <c r="B28" s="112" t="n"/>
-      <c r="C28" s="112" t="n"/>
+      <c r="A28" s="210" t="n"/>
+      <c r="B28" s="213" t="n"/>
+      <c r="C28" s="213" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="109" t="n"/>
-      <c r="B29" s="112" t="n"/>
-      <c r="C29" s="112" t="n"/>
+      <c r="A29" s="210" t="n"/>
+      <c r="B29" s="213" t="n"/>
+      <c r="C29" s="213" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="109" t="n"/>
-      <c r="B30" s="112" t="n"/>
-      <c r="C30" s="112" t="n"/>
+      <c r="A30" s="210" t="n"/>
+      <c r="B30" s="213" t="n"/>
+      <c r="C30" s="213" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="109" t="n"/>
-      <c r="B31" s="110" t="n"/>
-      <c r="C31" s="110" t="n"/>
+      <c r="A31" s="210" t="n"/>
+      <c r="B31" s="211" t="n"/>
+      <c r="C31" s="211" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="111" t="n"/>
-      <c r="B32" s="112" t="n"/>
-      <c r="C32" s="112" t="n"/>
+      <c r="A32" s="212" t="n"/>
+      <c r="B32" s="213" t="n"/>
+      <c r="C32" s="213" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="111" t="n"/>
-      <c r="B33" s="112" t="n"/>
-      <c r="C33" s="112" t="n"/>
+      <c r="A33" s="212" t="n"/>
+      <c r="B33" s="213" t="n"/>
+      <c r="C33" s="213" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="111" t="n"/>
-      <c r="B34" s="112" t="n"/>
-      <c r="C34" s="112" t="n"/>
+      <c r="A34" s="212" t="n"/>
+      <c r="B34" s="213" t="n"/>
+      <c r="C34" s="213" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="113" t="n"/>
-      <c r="B35" s="114" t="n"/>
-      <c r="C35" s="114" t="n"/>
+      <c r="A35" s="214" t="n"/>
+      <c r="B35" s="215" t="n"/>
+      <c r="C35" s="215" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="109" t="n"/>
-      <c r="B36" s="112" t="n"/>
-      <c r="C36" s="112" t="n"/>
+      <c r="A36" s="210" t="n"/>
+      <c r="B36" s="213" t="n"/>
+      <c r="C36" s="213" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="115" t="n"/>
-      <c r="B37" s="114" t="n"/>
-      <c r="C37" s="114" t="n"/>
+      <c r="A37" s="216" t="n"/>
+      <c r="B37" s="215" t="n"/>
+      <c r="C37" s="215" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="116" t="n"/>
-      <c r="B38" s="114" t="n"/>
-      <c r="C38" s="114" t="n"/>
+      <c r="A38" s="217" t="n"/>
+      <c r="B38" s="215" t="n"/>
+      <c r="C38" s="215" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="107" t="n"/>
+      <c r="A39" s="208" t="n"/>
+      <c r="B39" s="205" t="n"/>
+      <c r="C39" s="205" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="108" t="n"/>
-      <c r="B40" s="112" t="n"/>
-      <c r="C40" s="112" t="n"/>
+      <c r="A40" s="209" t="n"/>
+      <c r="B40" s="213" t="n"/>
+      <c r="C40" s="213" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="108" t="n"/>
-      <c r="B41" s="112" t="n"/>
-      <c r="C41" s="110" t="n"/>
+      <c r="A41" s="209" t="n"/>
+      <c r="B41" s="213" t="n"/>
+      <c r="C41" s="211" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="109" t="n"/>
-      <c r="B42" s="112" t="n"/>
-      <c r="C42" s="110" t="n"/>
+      <c r="A42" s="210" t="n"/>
+      <c r="B42" s="213" t="n"/>
+      <c r="C42" s="211" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="115" t="n"/>
-      <c r="B43" s="114" t="n"/>
-      <c r="C43" s="117" t="n"/>
+      <c r="A43" s="216" t="n"/>
+      <c r="B43" s="215" t="n"/>
+      <c r="C43" s="218" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="116" t="n"/>
-      <c r="B44" s="114" t="n"/>
-      <c r="C44" s="117" t="n"/>
+      <c r="A44" s="217" t="n"/>
+      <c r="B44" s="215" t="n"/>
+      <c r="C44" s="218" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="107" t="n"/>
+      <c r="A45" s="208" t="n"/>
+      <c r="B45" s="205" t="n"/>
+      <c r="C45" s="205" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="108" t="n"/>
-      <c r="B46" s="110" t="n"/>
-      <c r="C46" s="110" t="n"/>
+      <c r="A46" s="209" t="n"/>
+      <c r="B46" s="211" t="n"/>
+      <c r="C46" s="211" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="109" t="n"/>
-      <c r="B47" s="112" t="n"/>
-      <c r="C47" s="112" t="n"/>
+      <c r="A47" s="210" t="n"/>
+      <c r="B47" s="213" t="n"/>
+      <c r="C47" s="213" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="115" t="n"/>
-      <c r="B48" s="114" t="n"/>
-      <c r="C48" s="114" t="n"/>
+      <c r="A48" s="216" t="n"/>
+      <c r="B48" s="215" t="n"/>
+      <c r="C48" s="215" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="108" t="n"/>
-      <c r="B49" s="112" t="n"/>
-      <c r="C49" s="112" t="n"/>
+      <c r="A49" s="209" t="n"/>
+      <c r="B49" s="213" t="n"/>
+      <c r="C49" s="213" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="108" t="n"/>
-      <c r="B50" s="112" t="n"/>
-      <c r="C50" s="112" t="n"/>
+      <c r="A50" s="209" t="n"/>
+      <c r="B50" s="213" t="n"/>
+      <c r="C50" s="213" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="108" t="n"/>
-      <c r="B51" s="110" t="n"/>
-      <c r="C51" s="110" t="n"/>
+      <c r="A51" s="209" t="n"/>
+      <c r="B51" s="211" t="n"/>
+      <c r="C51" s="211" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="109" t="n"/>
-      <c r="B52" s="112" t="n"/>
-      <c r="C52" s="112" t="n"/>
+      <c r="A52" s="210" t="n"/>
+      <c r="B52" s="213" t="n"/>
+      <c r="C52" s="213" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="109" t="n"/>
-      <c r="B53" s="112" t="n"/>
-      <c r="C53" s="112" t="n"/>
+      <c r="A53" s="210" t="n"/>
+      <c r="B53" s="213" t="n"/>
+      <c r="C53" s="213" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="115" t="n"/>
-      <c r="B54" s="114" t="n"/>
-      <c r="C54" s="114" t="n"/>
+      <c r="A54" s="216" t="n"/>
+      <c r="B54" s="215" t="n"/>
+      <c r="C54" s="215" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="116" t="n"/>
-      <c r="B55" s="114" t="n"/>
-      <c r="C55" s="114" t="n"/>
+      <c r="A55" s="217" t="n"/>
+      <c r="B55" s="215" t="n"/>
+      <c r="C55" s="215" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="118" t="n"/>
-      <c r="B56" s="114" t="n"/>
-      <c r="C56" s="114" t="n"/>
+      <c r="A56" s="219" t="n"/>
+      <c r="B56" s="215" t="n"/>
+      <c r="C56" s="215" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="106" t="n"/>
+      <c r="A57" s="207" t="n"/>
+      <c r="B57" s="205" t="n"/>
+      <c r="C57" s="205" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="107" t="n"/>
+      <c r="A58" s="208" t="n"/>
+      <c r="B58" s="205" t="n"/>
+      <c r="C58" s="205" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="108" t="n"/>
+      <c r="A59" s="209" t="n"/>
+      <c r="B59" s="205" t="n"/>
+      <c r="C59" s="205" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="109" t="n"/>
+      <c r="A60" s="210" t="n"/>
+      <c r="B60" s="205" t="n"/>
+      <c r="C60" s="205" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="111" t="n"/>
-      <c r="B61" s="112" t="n"/>
-      <c r="C61" s="112" t="n"/>
+      <c r="A61" s="212" t="n"/>
+      <c r="B61" s="213" t="n"/>
+      <c r="C61" s="213" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="113" t="n"/>
-      <c r="B62" s="114" t="n"/>
-      <c r="C62" s="114" t="n"/>
+      <c r="A62" s="214" t="n"/>
+      <c r="B62" s="215" t="n"/>
+      <c r="C62" s="215" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="109" t="n"/>
+      <c r="A63" s="210" t="n"/>
+      <c r="B63" s="205" t="n"/>
+      <c r="C63" s="205" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="111" t="n"/>
-      <c r="B64" s="112" t="n"/>
-      <c r="C64" s="112" t="n"/>
+      <c r="A64" s="212" t="n"/>
+      <c r="B64" s="213" t="n"/>
+      <c r="C64" s="213" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="111" t="n"/>
-      <c r="B65" s="112" t="n"/>
-      <c r="C65" s="112" t="n"/>
+      <c r="A65" s="212" t="n"/>
+      <c r="B65" s="213" t="n"/>
+      <c r="C65" s="213" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="111" t="n"/>
-      <c r="B66" s="112" t="n"/>
-      <c r="C66" s="110" t="n"/>
+      <c r="A66" s="212" t="n"/>
+      <c r="B66" s="213" t="n"/>
+      <c r="C66" s="211" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="119" t="n"/>
-      <c r="B67" s="112" t="n"/>
-      <c r="C67" s="112" t="n"/>
+      <c r="A67" s="220" t="n"/>
+      <c r="B67" s="213" t="n"/>
+      <c r="C67" s="213" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="119" t="n"/>
-      <c r="B68" s="112" t="n"/>
-      <c r="C68" s="112" t="n"/>
+      <c r="A68" s="220" t="n"/>
+      <c r="B68" s="213" t="n"/>
+      <c r="C68" s="213" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="119" t="n"/>
-      <c r="B69" s="112" t="n"/>
-      <c r="C69" s="112" t="n"/>
+      <c r="A69" s="220" t="n"/>
+      <c r="B69" s="213" t="n"/>
+      <c r="C69" s="213" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="119" t="n"/>
-      <c r="B70" s="112" t="n"/>
-      <c r="C70" s="112" t="n"/>
+      <c r="A70" s="220" t="n"/>
+      <c r="B70" s="213" t="n"/>
+      <c r="C70" s="213" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="119" t="n"/>
-      <c r="B71" s="112" t="n"/>
-      <c r="C71" s="112" t="n"/>
+      <c r="A71" s="220" t="n"/>
+      <c r="B71" s="213" t="n"/>
+      <c r="C71" s="213" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="120" t="n"/>
-      <c r="B72" s="114" t="n"/>
-      <c r="C72" s="114" t="n"/>
+      <c r="A72" s="221" t="n"/>
+      <c r="B72" s="215" t="n"/>
+      <c r="C72" s="215" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="111" t="n"/>
-      <c r="B73" s="112" t="n"/>
-      <c r="C73" s="112" t="n"/>
+      <c r="A73" s="212" t="n"/>
+      <c r="B73" s="213" t="n"/>
+      <c r="C73" s="213" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="113" t="n"/>
-      <c r="B74" s="114" t="n"/>
-      <c r="C74" s="114" t="n"/>
+      <c r="A74" s="214" t="n"/>
+      <c r="B74" s="215" t="n"/>
+      <c r="C74" s="215" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="115" t="n"/>
-      <c r="B75" s="114" t="n"/>
-      <c r="C75" s="114" t="n"/>
+      <c r="A75" s="216" t="n"/>
+      <c r="B75" s="215" t="n"/>
+      <c r="C75" s="215" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="108" t="n"/>
+      <c r="A76" s="209" t="n"/>
+      <c r="B76" s="205" t="n"/>
+      <c r="C76" s="205" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="109" t="n"/>
-      <c r="B77" s="112" t="n"/>
-      <c r="C77" s="112" t="n"/>
+      <c r="A77" s="210" t="n"/>
+      <c r="B77" s="213" t="n"/>
+      <c r="C77" s="213" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="116" t="n"/>
-      <c r="B78" s="114" t="n"/>
-      <c r="C78" s="114" t="n"/>
+      <c r="A78" s="217" t="n"/>
+      <c r="B78" s="215" t="n"/>
+      <c r="C78" s="215" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="107" t="n"/>
+      <c r="A79" s="208" t="n"/>
+      <c r="B79" s="205" t="n"/>
+      <c r="C79" s="205" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="108" t="n"/>
-      <c r="B80" s="112" t="n"/>
-      <c r="C80" s="112" t="n"/>
+      <c r="A80" s="209" t="n"/>
+      <c r="B80" s="213" t="n"/>
+      <c r="C80" s="213" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="108" t="n"/>
-      <c r="B81" s="112" t="n"/>
-      <c r="C81" s="112" t="n"/>
+      <c r="A81" s="209" t="n"/>
+      <c r="B81" s="213" t="n"/>
+      <c r="C81" s="213" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="108" t="n"/>
-      <c r="B82" s="112" t="n"/>
-      <c r="C82" s="112" t="n"/>
+      <c r="A82" s="209" t="n"/>
+      <c r="B82" s="213" t="n"/>
+      <c r="C82" s="213" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="108" t="n"/>
-      <c r="B83" s="112" t="n"/>
-      <c r="C83" s="112" t="n"/>
+      <c r="A83" s="209" t="n"/>
+      <c r="B83" s="213" t="n"/>
+      <c r="C83" s="213" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="108" t="n"/>
-      <c r="B84" s="112" t="n"/>
-      <c r="C84" s="112" t="n"/>
+      <c r="A84" s="209" t="n"/>
+      <c r="B84" s="213" t="n"/>
+      <c r="C84" s="213" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="108" t="n"/>
-      <c r="B85" s="112" t="n"/>
-      <c r="C85" s="112" t="n"/>
+      <c r="A85" s="209" t="n"/>
+      <c r="B85" s="213" t="n"/>
+      <c r="C85" s="213" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="108" t="n"/>
-      <c r="B86" s="112" t="n"/>
-      <c r="C86" s="112" t="n"/>
+      <c r="A86" s="209" t="n"/>
+      <c r="B86" s="213" t="n"/>
+      <c r="C86" s="213" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="108" t="n"/>
-      <c r="B87" s="112" t="n"/>
-      <c r="C87" s="112" t="n"/>
+      <c r="A87" s="209" t="n"/>
+      <c r="B87" s="213" t="n"/>
+      <c r="C87" s="213" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="116" t="n"/>
-      <c r="B88" s="189" t="inlineStr">
+      <c r="A88" s="222" t="n"/>
+      <c r="B88" s="223" t="inlineStr">
         <is>
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="C88" s="114" t="n"/>
+      <c r="C88" s="224" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="118" t="n"/>
-      <c r="B89" s="189" t="inlineStr">
+      <c r="A89" s="225" t="n"/>
+      <c r="B89" s="223" t="inlineStr">
         <is>
           <t>Total L&amp;E</t>
         </is>
       </c>
-      <c r="C89" s="114" t="n"/>
+      <c r="C89" s="224" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="153" t="n"/>
@@ -12155,319 +12404,324 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="30" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" s="143">
-      <c r="A1" s="190" t="inlineStr">
+      <c r="A1" s="226" t="inlineStr">
         <is>
           <t>PASTE CLIENT P&amp;L FROM QUICKBOOKS HERE</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="143">
-      <c r="A2" s="191" t="inlineStr">
+      <c r="A2" s="227" t="inlineStr">
         <is>
           <t>Column A = Account Name, Column B = Amount (Current Year)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="143">
-      <c r="A3" s="191" t="inlineStr">
+      <c r="A3" s="227" t="inlineStr">
         <is>
           <t>Row 63: Net Income (this cell is referenced by formulas)</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="205" t="n"/>
+      <c r="B4" s="205" t="n"/>
+      <c r="C4" s="205" t="n"/>
+    </row>
     <row r="5" ht="15.75" customHeight="1" s="143">
-      <c r="A5" s="154" t="n"/>
-      <c r="B5" s="154" t="n"/>
-      <c r="C5" s="155" t="n"/>
+      <c r="A5" s="206" t="n"/>
+      <c r="B5" s="206" t="n"/>
+      <c r="C5" s="205" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1" s="143">
-      <c r="A6" s="121" t="n"/>
-      <c r="B6" s="105" t="n"/>
-      <c r="C6" s="154" t="n"/>
+      <c r="A6" s="228" t="n"/>
+      <c r="B6" s="206" t="n"/>
+      <c r="C6" s="206" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1" s="143">
-      <c r="A7" s="122" t="n"/>
-      <c r="B7" s="121" t="n"/>
-      <c r="C7" s="121" t="n"/>
+      <c r="A7" s="229" t="n"/>
+      <c r="B7" s="228" t="n"/>
+      <c r="C7" s="228" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="123" t="n"/>
-      <c r="B8" s="129" t="n"/>
-      <c r="C8" s="129" t="n"/>
+      <c r="A8" s="230" t="n"/>
+      <c r="B8" s="231" t="n"/>
+      <c r="C8" s="231" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="124" t="n"/>
-      <c r="B9" s="130" t="n"/>
-      <c r="C9" s="130" t="n"/>
+      <c r="A9" s="232" t="n"/>
+      <c r="B9" s="233" t="n"/>
+      <c r="C9" s="233" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="124" t="n"/>
-      <c r="B10" s="130" t="n"/>
-      <c r="C10" s="130" t="n"/>
+      <c r="A10" s="232" t="n"/>
+      <c r="B10" s="233" t="n"/>
+      <c r="C10" s="233" t="n"/>
     </row>
     <row r="11" ht="15.75" customHeight="1" s="143">
-      <c r="A11" s="122" t="n"/>
-      <c r="B11" s="121" t="n"/>
-      <c r="C11" s="121" t="n"/>
+      <c r="A11" s="229" t="n"/>
+      <c r="B11" s="228" t="n"/>
+      <c r="C11" s="228" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="123" t="n"/>
-      <c r="B12" s="131" t="n"/>
-      <c r="C12" s="131" t="n"/>
+      <c r="A12" s="230" t="n"/>
+      <c r="B12" s="234" t="n"/>
+      <c r="C12" s="234" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="125" t="n"/>
-      <c r="B13" s="129" t="n"/>
-      <c r="C13" s="129" t="n"/>
+      <c r="A13" s="235" t="n"/>
+      <c r="B13" s="231" t="n"/>
+      <c r="C13" s="231" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="125" t="n"/>
-      <c r="B14" s="129" t="n"/>
-      <c r="C14" s="129" t="n"/>
+      <c r="A14" s="235" t="n"/>
+      <c r="B14" s="231" t="n"/>
+      <c r="C14" s="231" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="125" t="n"/>
-      <c r="B15" s="129" t="n"/>
-      <c r="C15" s="129" t="n"/>
+      <c r="A15" s="235" t="n"/>
+      <c r="B15" s="231" t="n"/>
+      <c r="C15" s="231" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="125" t="n"/>
-      <c r="B16" s="129" t="n"/>
-      <c r="C16" s="129" t="n"/>
+      <c r="A16" s="235" t="n"/>
+      <c r="B16" s="231" t="n"/>
+      <c r="C16" s="231" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="125" t="n"/>
-      <c r="B17" s="129" t="n"/>
-      <c r="C17" s="129" t="n"/>
+      <c r="A17" s="235" t="n"/>
+      <c r="B17" s="231" t="n"/>
+      <c r="C17" s="231" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="125" t="n"/>
-      <c r="B18" s="129" t="n"/>
-      <c r="C18" s="129" t="n"/>
+      <c r="A18" s="235" t="n"/>
+      <c r="B18" s="231" t="n"/>
+      <c r="C18" s="231" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="125" t="n"/>
-      <c r="B19" s="131" t="n"/>
-      <c r="C19" s="129" t="n"/>
+      <c r="A19" s="235" t="n"/>
+      <c r="B19" s="234" t="n"/>
+      <c r="C19" s="231" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="125" t="n"/>
-      <c r="B20" s="131" t="n"/>
-      <c r="C20" s="129" t="n"/>
+      <c r="A20" s="235" t="n"/>
+      <c r="B20" s="234" t="n"/>
+      <c r="C20" s="231" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="126" t="n"/>
-      <c r="B21" s="130" t="n"/>
-      <c r="C21" s="130" t="n"/>
+      <c r="A21" s="236" t="n"/>
+      <c r="B21" s="233" t="n"/>
+      <c r="C21" s="233" t="n"/>
     </row>
     <row r="22" ht="23.25" customHeight="1" s="143">
-      <c r="A22" s="123" t="n"/>
-      <c r="B22" s="131" t="n"/>
-      <c r="C22" s="131" t="n"/>
+      <c r="A22" s="230" t="n"/>
+      <c r="B22" s="234" t="n"/>
+      <c r="C22" s="234" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="125" t="n"/>
-      <c r="B23" s="131" t="n"/>
-      <c r="C23" s="131" t="n"/>
+      <c r="A23" s="235" t="n"/>
+      <c r="B23" s="234" t="n"/>
+      <c r="C23" s="234" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="127" t="n"/>
-      <c r="B24" s="129" t="n"/>
-      <c r="C24" s="131" t="n"/>
+      <c r="A24" s="237" t="n"/>
+      <c r="B24" s="231" t="n"/>
+      <c r="C24" s="234" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="128" t="n"/>
-      <c r="B25" s="130" t="n"/>
-      <c r="C25" s="132" t="n"/>
+      <c r="A25" s="238" t="n"/>
+      <c r="B25" s="233" t="n"/>
+      <c r="C25" s="239" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="125" t="n"/>
-      <c r="B26" s="131" t="n"/>
-      <c r="C26" s="131" t="n"/>
+      <c r="A26" s="235" t="n"/>
+      <c r="B26" s="234" t="n"/>
+      <c r="C26" s="234" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="127" t="n"/>
-      <c r="B27" s="129" t="n"/>
-      <c r="C27" s="129" t="n"/>
+      <c r="A27" s="237" t="n"/>
+      <c r="B27" s="231" t="n"/>
+      <c r="C27" s="231" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="128" t="n"/>
-      <c r="B28" s="130" t="n"/>
-      <c r="C28" s="130" t="n"/>
+      <c r="A28" s="238" t="n"/>
+      <c r="B28" s="233" t="n"/>
+      <c r="C28" s="233" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="125" t="n"/>
-      <c r="B29" s="131" t="n"/>
-      <c r="C29" s="131" t="n"/>
+      <c r="A29" s="235" t="n"/>
+      <c r="B29" s="234" t="n"/>
+      <c r="C29" s="234" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="127" t="n"/>
-      <c r="B30" s="129" t="n"/>
-      <c r="C30" s="129" t="n"/>
+      <c r="A30" s="237" t="n"/>
+      <c r="B30" s="231" t="n"/>
+      <c r="C30" s="231" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="128" t="n"/>
-      <c r="B31" s="130" t="n"/>
-      <c r="C31" s="130" t="n"/>
+      <c r="A31" s="238" t="n"/>
+      <c r="B31" s="233" t="n"/>
+      <c r="C31" s="233" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="125" t="n"/>
-      <c r="B32" s="131" t="n"/>
-      <c r="C32" s="131" t="n"/>
+      <c r="A32" s="235" t="n"/>
+      <c r="B32" s="234" t="n"/>
+      <c r="C32" s="234" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="127" t="n"/>
-      <c r="B33" s="129" t="n"/>
-      <c r="C33" s="129" t="n"/>
+      <c r="A33" s="237" t="n"/>
+      <c r="B33" s="231" t="n"/>
+      <c r="C33" s="231" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="128" t="n"/>
-      <c r="B34" s="130" t="n"/>
-      <c r="C34" s="130" t="n"/>
+      <c r="A34" s="238" t="n"/>
+      <c r="B34" s="233" t="n"/>
+      <c r="C34" s="233" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="125" t="n"/>
-      <c r="B35" s="131" t="n"/>
-      <c r="C35" s="131" t="n"/>
+      <c r="A35" s="235" t="n"/>
+      <c r="B35" s="234" t="n"/>
+      <c r="C35" s="234" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="127" t="n"/>
-      <c r="B36" s="129" t="n"/>
-      <c r="C36" s="129" t="n"/>
+      <c r="A36" s="237" t="n"/>
+      <c r="B36" s="231" t="n"/>
+      <c r="C36" s="231" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="127" t="n"/>
-      <c r="B37" s="129" t="n"/>
-      <c r="C37" s="129" t="n"/>
+      <c r="A37" s="237" t="n"/>
+      <c r="B37" s="231" t="n"/>
+      <c r="C37" s="231" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="127" t="n"/>
-      <c r="B38" s="129" t="n"/>
-      <c r="C38" s="129" t="n"/>
+      <c r="A38" s="237" t="n"/>
+      <c r="B38" s="231" t="n"/>
+      <c r="C38" s="231" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="127" t="n"/>
-      <c r="B39" s="129" t="n"/>
-      <c r="C39" s="129" t="n"/>
+      <c r="A39" s="237" t="n"/>
+      <c r="B39" s="231" t="n"/>
+      <c r="C39" s="231" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="127" t="n"/>
-      <c r="B40" s="131" t="n"/>
-      <c r="C40" s="129" t="n"/>
+      <c r="A40" s="237" t="n"/>
+      <c r="B40" s="234" t="n"/>
+      <c r="C40" s="231" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="128" t="n"/>
-      <c r="B41" s="130" t="n"/>
-      <c r="C41" s="130" t="n"/>
+      <c r="A41" s="238" t="n"/>
+      <c r="B41" s="233" t="n"/>
+      <c r="C41" s="233" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="125" t="n"/>
-      <c r="B42" s="129" t="n"/>
-      <c r="C42" s="129" t="n"/>
+      <c r="A42" s="235" t="n"/>
+      <c r="B42" s="231" t="n"/>
+      <c r="C42" s="231" t="n"/>
     </row>
     <row r="43" ht="23.25" customHeight="1" s="143">
-      <c r="A43" s="126" t="n"/>
-      <c r="B43" s="130" t="n"/>
-      <c r="C43" s="130" t="n"/>
+      <c r="A43" s="236" t="n"/>
+      <c r="B43" s="233" t="n"/>
+      <c r="C43" s="233" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="123" t="n"/>
-      <c r="B44" s="129" t="n"/>
-      <c r="C44" s="131" t="n"/>
+      <c r="A44" s="230" t="n"/>
+      <c r="B44" s="231" t="n"/>
+      <c r="C44" s="234" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="123" t="n"/>
-      <c r="B45" s="129" t="n"/>
-      <c r="C45" s="129" t="n"/>
+      <c r="A45" s="230" t="n"/>
+      <c r="B45" s="231" t="n"/>
+      <c r="C45" s="231" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="123" t="n"/>
-      <c r="B46" s="129" t="n"/>
-      <c r="C46" s="129" t="n"/>
+      <c r="A46" s="230" t="n"/>
+      <c r="B46" s="231" t="n"/>
+      <c r="C46" s="231" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="123" t="n"/>
-      <c r="B47" s="129" t="n"/>
-      <c r="C47" s="131" t="n"/>
+      <c r="A47" s="230" t="n"/>
+      <c r="B47" s="231" t="n"/>
+      <c r="C47" s="234" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="123" t="n"/>
-      <c r="B48" s="129" t="n"/>
-      <c r="C48" s="129" t="n"/>
+      <c r="A48" s="230" t="n"/>
+      <c r="B48" s="231" t="n"/>
+      <c r="C48" s="231" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="123" t="n"/>
-      <c r="B49" s="129" t="n"/>
-      <c r="C49" s="131" t="n"/>
+      <c r="A49" s="230" t="n"/>
+      <c r="B49" s="231" t="n"/>
+      <c r="C49" s="234" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="124" t="n"/>
-      <c r="B50" s="130" t="n"/>
-      <c r="C50" s="130" t="n"/>
+      <c r="A50" s="232" t="n"/>
+      <c r="B50" s="233" t="n"/>
+      <c r="C50" s="233" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="124" t="n"/>
-      <c r="B51" s="130" t="n"/>
-      <c r="C51" s="130" t="n"/>
+      <c r="A51" s="232" t="n"/>
+      <c r="B51" s="233" t="n"/>
+      <c r="C51" s="233" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="143">
-      <c r="A52" s="122" t="n"/>
-      <c r="B52" s="121" t="n"/>
-      <c r="C52" s="121" t="n"/>
+      <c r="A52" s="229" t="n"/>
+      <c r="B52" s="228" t="n"/>
+      <c r="C52" s="228" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="123" t="n"/>
-      <c r="B53" s="129" t="n"/>
-      <c r="C53" s="129" t="n"/>
+      <c r="A53" s="230" t="n"/>
+      <c r="B53" s="231" t="n"/>
+      <c r="C53" s="231" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="123" t="n"/>
-      <c r="B54" s="129" t="n"/>
-      <c r="C54" s="129" t="n"/>
+      <c r="A54" s="230" t="n"/>
+      <c r="B54" s="231" t="n"/>
+      <c r="C54" s="231" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="123" t="n"/>
-      <c r="B55" s="129" t="n"/>
-      <c r="C55" s="129" t="n"/>
+      <c r="A55" s="230" t="n"/>
+      <c r="B55" s="231" t="n"/>
+      <c r="C55" s="231" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="123" t="n"/>
-      <c r="B56" s="129" t="n"/>
-      <c r="C56" s="131" t="n"/>
+      <c r="A56" s="230" t="n"/>
+      <c r="B56" s="231" t="n"/>
+      <c r="C56" s="234" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="124" t="n"/>
-      <c r="B57" s="130" t="n"/>
-      <c r="C57" s="130" t="n"/>
+      <c r="A57" s="232" t="n"/>
+      <c r="B57" s="233" t="n"/>
+      <c r="C57" s="233" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="143">
-      <c r="A58" s="122" t="n"/>
-      <c r="B58" s="121" t="n"/>
-      <c r="C58" s="121" t="n"/>
+      <c r="A58" s="229" t="n"/>
+      <c r="B58" s="228" t="n"/>
+      <c r="C58" s="228" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="123" t="n"/>
-      <c r="B59" s="129" t="n"/>
-      <c r="C59" s="131" t="n"/>
+      <c r="A59" s="230" t="n"/>
+      <c r="B59" s="231" t="n"/>
+      <c r="C59" s="234" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="123" t="n"/>
-      <c r="B60" s="129" t="n"/>
-      <c r="C60" s="131" t="n"/>
+      <c r="A60" s="230" t="n"/>
+      <c r="B60" s="231" t="n"/>
+      <c r="C60" s="234" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="124" t="n"/>
-      <c r="B61" s="130" t="n"/>
-      <c r="C61" s="132" t="n"/>
+      <c r="A61" s="232" t="n"/>
+      <c r="B61" s="233" t="n"/>
+      <c r="C61" s="239" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="124" t="n"/>
-      <c r="B62" s="130" t="n"/>
-      <c r="C62" s="130" t="n"/>
+      <c r="A62" s="232" t="n"/>
+      <c r="B62" s="233" t="n"/>
+      <c r="C62" s="233" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="124" t="n"/>
-      <c r="B63" s="192" t="inlineStr">
+      <c r="A63" s="240" t="n"/>
+      <c r="B63" s="241" t="inlineStr">
         <is>
           <t>Net Income goes here</t>
         </is>
@@ -12603,7 +12857,7 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="143">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="200" t="inlineStr">
         <is>
           <t>ASSETS (from PBC Balance Sheet — Sch L)</t>
         </is>
@@ -12832,34 +13086,34 @@
       <c r="J14" s="63" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="143">
-      <c r="A15" s="64" t="inlineStr">
+      <c r="A15" s="242" t="inlineStr">
         <is>
           <t>Total Current Assets</t>
         </is>
       </c>
-      <c r="B15">
+      <c r="B15" s="243">
         <f>SUM(B8:B14)</f>
         <v/>
       </c>
-      <c r="C15">
+      <c r="C15" s="243">
         <f>SUM(C8:C14)</f>
         <v/>
       </c>
-      <c r="D15" s="32">
+      <c r="D15" s="202">
         <f>SUM(D8:D14)</f>
         <v/>
       </c>
       <c r="E15" s="32" t="n"/>
-      <c r="F15" s="32">
+      <c r="F15" s="202">
         <f>SUM(F8:F14)</f>
         <v/>
       </c>
-      <c r="G15" s="64" t="inlineStr">
+      <c r="G15" s="244" t="inlineStr">
         <is>
           <t>Sch L, Ln 1-7</t>
         </is>
       </c>
-      <c r="H15" s="32">
+      <c r="H15" s="202">
         <f>SUM(H8:H14)</f>
         <v/>
       </c>
@@ -12938,34 +13192,34 @@
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="143">
-      <c r="A19" s="64" t="inlineStr">
+      <c r="A19" s="242" t="inlineStr">
         <is>
           <t>Total Investments</t>
         </is>
       </c>
-      <c r="B19">
+      <c r="B19" s="243">
         <f>SUM(B17:B18)</f>
         <v/>
       </c>
-      <c r="C19">
+      <c r="C19" s="243">
         <f>SUM(C17:C18)</f>
         <v/>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="202">
         <f>SUM(D17:D18)</f>
         <v/>
       </c>
       <c r="E19" s="32" t="n"/>
-      <c r="F19" s="32">
+      <c r="F19" s="202">
         <f>SUM(F17:F18)</f>
         <v/>
       </c>
-      <c r="G19" s="64" t="inlineStr">
+      <c r="G19" s="244" t="inlineStr">
         <is>
           <t>Sch L, Ln 8</t>
         </is>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="202">
         <f>SUM(H17:H18)</f>
         <v/>
       </c>
@@ -13230,34 +13484,34 @@
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="143">
-      <c r="A29" s="64" t="inlineStr">
+      <c r="A29" s="242" t="inlineStr">
         <is>
           <t>Total Fixed Assets (Net)</t>
         </is>
       </c>
-      <c r="B29">
+      <c r="B29" s="243">
         <f>SUM(B21:B28)</f>
         <v/>
       </c>
-      <c r="C29">
+      <c r="C29" s="243">
         <f>SUM(C21:C28)</f>
         <v/>
       </c>
-      <c r="D29" s="32">
+      <c r="D29" s="202">
         <f>SUM(D21:D28)</f>
         <v/>
       </c>
       <c r="E29" s="32" t="n"/>
-      <c r="F29" s="32">
+      <c r="F29" s="202">
         <f>SUM(F21:F28)</f>
         <v/>
       </c>
-      <c r="G29" s="64" t="inlineStr">
+      <c r="G29" s="244" t="inlineStr">
         <is>
           <t>Sch L, Ln 10c</t>
         </is>
       </c>
-      <c r="H29" s="32">
+      <c r="H29" s="202">
         <f>SUM(H21:H28)</f>
         <v/>
       </c>
@@ -13332,34 +13586,34 @@
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="143">
-      <c r="A33" s="64" t="inlineStr">
+      <c r="A33" s="242" t="inlineStr">
         <is>
           <t>Total Other Assets</t>
         </is>
       </c>
-      <c r="B33">
+      <c r="B33" s="243">
         <f>SUM(B31:B32)</f>
         <v/>
       </c>
-      <c r="C33">
+      <c r="C33" s="243">
         <f>SUM(C31:C32)</f>
         <v/>
       </c>
-      <c r="D33" s="32">
+      <c r="D33" s="202">
         <f>SUM(D31:D32)</f>
         <v/>
       </c>
       <c r="E33" s="32" t="n"/>
-      <c r="F33" s="32">
+      <c r="F33" s="202">
         <f>SUM(F31:F32)</f>
         <v/>
       </c>
-      <c r="G33" s="64" t="inlineStr">
+      <c r="G33" s="244" t="inlineStr">
         <is>
           <t>Sch L, Ln 13</t>
         </is>
       </c>
-      <c r="H33" s="32">
+      <c r="H33" s="202">
         <f>SUM(H31:H32)</f>
         <v/>
       </c>
@@ -13368,29 +13622,29 @@
     </row>
     <row r="34" ht="15" customHeight="1" s="143"/>
     <row r="35" ht="15" customHeight="1" s="143">
-      <c r="A35" s="65" t="inlineStr">
+      <c r="A35" s="242" t="inlineStr">
         <is>
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B35">
+      <c r="B35" s="243">
         <f>B15+B19+B29+B33</f>
         <v/>
       </c>
-      <c r="C35">
+      <c r="C35" s="243">
         <f>C15+C19+C29+C33</f>
         <v/>
       </c>
-      <c r="D35" s="39">
+      <c r="D35" s="245">
         <f>D15+D19+D29+D33</f>
         <v/>
       </c>
       <c r="E35" s="66" t="n"/>
-      <c r="F35" s="39">
+      <c r="F35" s="245">
         <f>F15+F19+F29+F33</f>
         <v/>
       </c>
-      <c r="G35" s="66" t="inlineStr">
+      <c r="G35" s="243" t="inlineStr">
         <is>
           <t>Sch L, Ln 15</t>
         </is>
@@ -13401,7 +13655,7 @@
     </row>
     <row r="36" ht="15" customHeight="1" s="143"/>
     <row r="37" ht="15" customHeight="1" s="143">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="200" t="inlineStr">
         <is>
           <t>LIABILITIES (from PBC Balance Sheet — Sch L)</t>
         </is>
@@ -13601,7 +13855,7 @@
       <c r="J43" s="63" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="143">
-      <c r="A44" s="60" t="inlineStr">
+      <c r="A44" s="246" t="inlineStr">
         <is>
           <t>Other liabilities</t>
         </is>
@@ -13700,34 +13954,34 @@
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="143">
-      <c r="A47" s="64" t="inlineStr">
+      <c r="A47" s="242" t="inlineStr">
         <is>
           <t>TOTAL LIABILITIES</t>
         </is>
       </c>
-      <c r="B47">
+      <c r="B47" s="243">
         <f>SUM(B38:B46)</f>
         <v/>
       </c>
-      <c r="C47">
+      <c r="C47" s="243">
         <f>SUM(C38:C46)</f>
         <v/>
       </c>
-      <c r="D47" s="32">
+      <c r="D47" s="202">
         <f>SUM(D38:D46)</f>
         <v/>
       </c>
       <c r="E47" s="32" t="n"/>
-      <c r="F47" s="32">
+      <c r="F47" s="202">
         <f>SUM(F38:F46)</f>
         <v/>
       </c>
-      <c r="G47" s="64" t="inlineStr">
+      <c r="G47" s="244" t="inlineStr">
         <is>
           <t>Sch L, Ln 20</t>
         </is>
       </c>
-      <c r="H47" s="32">
+      <c r="H47" s="202">
         <f>SUM(H38:H46)</f>
         <v/>
       </c>
@@ -13736,7 +13990,7 @@
     </row>
     <row r="48" ht="15" customHeight="1" s="143"/>
     <row r="49" ht="15" customHeight="1" s="143">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="200" t="inlineStr">
         <is>
           <t>EQUITY (from PBC Balance Sheet — Sch L)</t>
         </is>
@@ -13952,34 +14206,34 @@
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="143">
-      <c r="A56" s="64" t="inlineStr">
+      <c r="A56" s="242" t="inlineStr">
         <is>
           <t>TOTAL EQUITY</t>
         </is>
       </c>
-      <c r="B56">
+      <c r="B56" s="243">
         <f>SUM(B50:B55)</f>
         <v/>
       </c>
-      <c r="C56">
+      <c r="C56" s="243">
         <f>SUM(C50:C55)</f>
         <v/>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="202">
         <f>SUM(D50:D55)</f>
         <v/>
       </c>
       <c r="E56" s="32" t="n"/>
-      <c r="F56" s="32">
+      <c r="F56" s="202">
         <f>SUM(F50:F55)</f>
         <v/>
       </c>
-      <c r="G56" s="64" t="inlineStr">
+      <c r="G56" s="244" t="inlineStr">
         <is>
           <t>Sch L, Ln 25</t>
         </is>
       </c>
-      <c r="H56" s="32">
+      <c r="H56" s="202">
         <f>SUM(H50:H55)</f>
         <v/>
       </c>
@@ -13988,25 +14242,25 @@
     </row>
     <row r="57" ht="15" customHeight="1" s="143"/>
     <row r="58" ht="15" customHeight="1" s="143">
-      <c r="A58" s="65" t="inlineStr">
+      <c r="A58" s="242" t="inlineStr">
         <is>
           <t>TOTAL LIABILITIES &amp; EQUITY</t>
         </is>
       </c>
-      <c r="B58">
+      <c r="B58" s="243">
         <f>B47+B56</f>
         <v/>
       </c>
-      <c r="C58">
+      <c r="C58" s="243">
         <f>C47+C56</f>
         <v/>
       </c>
-      <c r="D58" s="39">
+      <c r="D58" s="245">
         <f>D47+D56</f>
         <v/>
       </c>
       <c r="E58" s="66" t="n"/>
-      <c r="F58" s="39">
+      <c r="F58" s="245">
         <f>F47+F56</f>
         <v/>
       </c>
@@ -14016,24 +14270,24 @@
       <c r="J58" s="66" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1" s="143">
-      <c r="A59" s="145" t="inlineStr">
+      <c r="A59" s="201" t="inlineStr">
         <is>
           <t>CHECK: Total Assets − Total L&amp;E (should be zero)</t>
         </is>
       </c>
-      <c r="B59">
+      <c r="B59" s="243">
         <f>B35-B58</f>
         <v/>
       </c>
-      <c r="C59">
+      <c r="C59" s="243">
         <f>C35-C58</f>
         <v/>
       </c>
-      <c r="D59" s="17">
+      <c r="D59" s="247">
         <f>D35-D58</f>
         <v/>
       </c>
-      <c r="F59">
+      <c r="F59" s="243">
         <f>F35-F58</f>
         <v/>
       </c>
@@ -14041,14 +14295,14 @@
     <row r="60" ht="15" customHeight="1" s="143"/>
     <row r="61" ht="15" customHeight="1" s="143"/>
     <row r="62" ht="15" customHeight="1" s="143">
-      <c r="A62" s="162" t="inlineStr">
+      <c r="A62" s="248" t="inlineStr">
         <is>
           <t>INCOME STATEMENT — BOOK-TO-TAX ADJUSTMENTS</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="143">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="200" t="inlineStr">
         <is>
           <t>INCOME</t>
         </is>
@@ -14062,28 +14316,28 @@
       <c r="J63" s="8" t="n"/>
     </row>
     <row r="64" ht="15" customHeight="1" s="143">
-      <c r="A64" s="60" t="inlineStr">
+      <c r="A64" s="249" t="inlineStr">
         <is>
           <t>Gross Receipts - Consulting</t>
         </is>
       </c>
-      <c r="B64" s="10">
+      <c r="B64" s="250">
         <f>'P&amp;L'!B7</f>
         <v/>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" s="243" t="n">
         <v>0</v>
       </c>
-      <c r="D64" s="61">
+      <c r="D64" s="251">
         <f>B64+C64</f>
         <v/>
       </c>
       <c r="E64" s="61" t="n"/>
-      <c r="F64" s="61">
+      <c r="F64" s="251">
         <f>D64+E64</f>
         <v/>
       </c>
-      <c r="G64" s="62" t="inlineStr">
+      <c r="G64" s="252" t="inlineStr">
         <is>
           <t>Pg 1, Line 1a</t>
         </is>
@@ -14093,28 +14347,28 @@
       <c r="J64" s="63" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1" s="143">
-      <c r="A65" s="60" t="inlineStr">
+      <c r="A65" s="249" t="inlineStr">
         <is>
           <t>Gross Receipts - Software Licensing</t>
         </is>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="250">
         <f>'P&amp;L'!B8</f>
         <v/>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" s="243" t="n">
         <v>0</v>
       </c>
-      <c r="D65" s="61">
+      <c r="D65" s="251">
         <f>B65+C65</f>
         <v/>
       </c>
       <c r="E65" s="61" t="n"/>
-      <c r="F65" s="61">
+      <c r="F65" s="251">
         <f>D65+E65</f>
         <v/>
       </c>
-      <c r="G65" s="62" t="inlineStr">
+      <c r="G65" s="252" t="inlineStr">
         <is>
           <t>Pg 1, Line 1a</t>
         </is>
@@ -14277,30 +14531,30 @@
       <c r="J73" s="77" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1" s="143">
-      <c r="A74" s="64" t="inlineStr">
+      <c r="A74" s="242" t="inlineStr">
         <is>
           <t>TOTAL INCOME (per WTB)</t>
         </is>
       </c>
-      <c r="B74">
+      <c r="B74" s="243">
         <f>SUM(B64:B67)</f>
         <v/>
       </c>
-      <c r="C74">
+      <c r="C74" s="243">
         <f>SUM(C64:C67)</f>
         <v/>
       </c>
-      <c r="D74" s="32">
+      <c r="D74" s="202">
         <f>SUM(D64:D67)</f>
         <v/>
       </c>
       <c r="E74" s="32" t="n"/>
-      <c r="F74" s="32">
+      <c r="F74" s="202">
         <f>SUM(F64:F67)</f>
         <v/>
       </c>
       <c r="G74" s="64" t="n"/>
-      <c r="H74" s="32">
+      <c r="H74" s="202">
         <f>SUM(H64:H73)</f>
         <v/>
       </c>
@@ -14309,7 +14563,7 @@
     </row>
     <row r="75" ht="15" customHeight="1" s="143"/>
     <row r="76" ht="15" customHeight="1" s="143">
-      <c r="A76" s="8" t="inlineStr">
+      <c r="A76" s="200" t="inlineStr">
         <is>
           <t>COST OF GOODS SOLD</t>
         </is>
@@ -14420,34 +14674,34 @@
       <c r="J79" s="63" t="n"/>
     </row>
     <row r="80" ht="15" customHeight="1" s="143">
-      <c r="A80" s="64" t="inlineStr">
+      <c r="A80" s="242" t="inlineStr">
         <is>
           <t>TOTAL COGS</t>
         </is>
       </c>
-      <c r="B80">
+      <c r="B80" s="243">
         <f>SUM(B77:B79)</f>
         <v/>
       </c>
-      <c r="C80">
+      <c r="C80" s="243">
         <f>SUM(C77:C79)</f>
         <v/>
       </c>
-      <c r="D80" s="32">
+      <c r="D80" s="202">
         <f>SUM(D77:D79)</f>
         <v/>
       </c>
       <c r="E80" s="32" t="n"/>
-      <c r="F80" s="32">
+      <c r="F80" s="202">
         <f>SUM(F77:F79)</f>
         <v/>
       </c>
-      <c r="G80" s="64" t="inlineStr">
+      <c r="G80" s="244" t="inlineStr">
         <is>
           <t>Pg 1, Line 2</t>
         </is>
       </c>
-      <c r="H80" s="32">
+      <c r="H80" s="202">
         <f>SUM(H77:H79)</f>
         <v/>
       </c>
@@ -14456,7 +14710,7 @@
     </row>
     <row r="81" ht="15" customHeight="1" s="143"/>
     <row r="82" ht="15" customHeight="1" s="143">
-      <c r="A82" s="8" t="inlineStr">
+      <c r="A82" s="200" t="inlineStr">
         <is>
           <t>OFFICER COMPENSATION</t>
         </is>
@@ -14470,7 +14724,7 @@
       <c r="J82" s="8" t="n"/>
     </row>
     <row r="83" ht="27.75" customHeight="1" s="143">
-      <c r="A83" s="60" t="inlineStr">
+      <c r="A83" s="246" t="inlineStr">
         <is>
           <t>Officer Comp - [SH1 Name] ([Title], [%]%)</t>
         </is>
@@ -14500,7 +14754,7 @@
       </c>
     </row>
     <row r="84" ht="27.75" customHeight="1" s="143">
-      <c r="A84" s="60" t="inlineStr">
+      <c r="A84" s="246" t="inlineStr">
         <is>
           <t>Officer Comp - [SH2 Name] ([Title], [%]%)</t>
         </is>
@@ -14532,30 +14786,30 @@
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="143">
-      <c r="A85" s="64" t="inlineStr">
+      <c r="A85" s="242" t="inlineStr">
         <is>
           <t>TOTAL OFFICER COMP</t>
         </is>
       </c>
-      <c r="B85">
+      <c r="B85" s="243">
         <f>SUM(B83:B84)</f>
         <v/>
       </c>
-      <c r="D85" s="32">
+      <c r="D85" s="202">
         <f>SUM(D83:D84)</f>
         <v/>
       </c>
       <c r="E85" s="32" t="n"/>
-      <c r="F85" s="32">
+      <c r="F85" s="202">
         <f>SUM(F83:F84)</f>
         <v/>
       </c>
-      <c r="G85" s="64" t="inlineStr">
+      <c r="G85" s="244" t="inlineStr">
         <is>
           <t>Pg 1, Line 7</t>
         </is>
       </c>
-      <c r="H85" s="32">
+      <c r="H85" s="202">
         <f>SUM(H83:H84)</f>
         <v/>
       </c>
@@ -14564,7 +14818,7 @@
     </row>
     <row r="86" ht="15" customHeight="1" s="143"/>
     <row r="87" ht="15" customHeight="1" s="143">
-      <c r="A87" s="8" t="inlineStr">
+      <c r="A87" s="200" t="inlineStr">
         <is>
           <t>DEDUCTIONS</t>
         </is>
@@ -15795,7 +16049,7 @@
       <c r="J120" s="63" t="n"/>
     </row>
     <row r="121" ht="27.75" customHeight="1" s="143">
-      <c r="A121" s="71" t="inlineStr">
+      <c r="A121" s="253" t="inlineStr">
         <is>
           <t>Rental Activity Expenses (Equipment)</t>
         </is>
@@ -15896,7 +16150,7 @@
       <c r="H125" s="31" t="n"/>
     </row>
     <row r="126" ht="27.75" customHeight="1" s="143">
-      <c r="A126" s="35" t="inlineStr">
+      <c r="A126" s="254" t="inlineStr">
         <is>
           <t>Officer Salary Adjustment</t>
         </is>
@@ -15963,35 +16217,35 @@
     </row>
     <row r="129" ht="15" customHeight="1" s="143"/>
     <row r="130" ht="15" customHeight="1" s="143">
-      <c r="A130" s="64" t="inlineStr">
+      <c r="A130" s="242" t="inlineStr">
         <is>
           <t>TOTAL DEDUCTIONS (per WTB)</t>
         </is>
       </c>
-      <c r="B130">
+      <c r="B130" s="243">
         <f>SUM(B88:B129)</f>
         <v/>
       </c>
-      <c r="C130">
+      <c r="C130" s="243">
         <f>SUM(C88:C129)</f>
         <v/>
       </c>
-      <c r="D130" s="32">
+      <c r="D130" s="202">
         <f>SUM(D88:D129)</f>
         <v/>
       </c>
-      <c r="F130" s="32">
+      <c r="F130" s="202">
         <f>SUM(F88:F129)</f>
         <v/>
       </c>
-      <c r="H130" s="32">
+      <c r="H130" s="202">
         <f>SUM(H88:H129)</f>
         <v/>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="143"/>
     <row r="132" ht="15" customHeight="1" s="143">
-      <c r="A132" s="164" t="inlineStr">
+      <c r="A132" s="255" t="inlineStr">
         <is>
           <t>OTHER INCOME / (EXPENSE) — Schedule K &amp; M-1 Items</t>
         </is>
@@ -16052,41 +16306,41 @@
       <c r="L133" s="164" t="n"/>
     </row>
     <row r="134" ht="15" customHeight="1" s="143">
-      <c r="A134" s="164" t="inlineStr">
+      <c r="A134" s="256" t="inlineStr">
         <is>
           <t>Ordinary Dividends – Schwab One (K-5a)</t>
         </is>
       </c>
-      <c r="B134" s="164">
+      <c r="B134" s="257">
         <f>'P&amp;L'!B54</f>
         <v/>
       </c>
-      <c r="C134" s="164" t="n">
+      <c r="C134" s="257" t="n">
         <v>0</v>
       </c>
-      <c r="D134" s="164">
+      <c r="D134" s="257">
         <f>B134+C134</f>
         <v/>
       </c>
-      <c r="E134" s="164">
+      <c r="E134" s="257">
         <f>F134-D134</f>
         <v/>
       </c>
       <c r="F134" s="196" t="n"/>
-      <c r="G134" s="164" t="inlineStr">
+      <c r="G134" s="257" t="inlineStr">
         <is>
           <t>→ Sch K, Ln 5a / 5b</t>
         </is>
       </c>
-      <c r="H134" s="164" t="n">
+      <c r="H134" s="257" t="n">
         <v>0</v>
       </c>
-      <c r="I134" s="164" t="inlineStr">
+      <c r="I134" s="257" t="inlineStr">
         <is>
           <t>K-5a / K-5b</t>
         </is>
       </c>
-      <c r="J134" s="164" t="inlineStr">
+      <c r="J134" s="257" t="inlineStr">
         <is>
           <t>Ordinary divs → K-5a. Qualified portion → K-5b. ⚑ TBD: pull K-5b from 1099-DIV Box 1b.</t>
         </is>
@@ -16213,29 +16467,29 @@
       <c r="L138" s="164" t="n"/>
     </row>
     <row r="139" ht="15" customHeight="1" s="143">
-      <c r="A139" s="164" t="inlineStr">
+      <c r="A139" s="256" t="inlineStr">
         <is>
           <t>TOTAL OTHER INCOME (net book)</t>
         </is>
       </c>
-      <c r="B139" s="164">
+      <c r="B139" s="257">
         <f>SUM(B133:B137)</f>
         <v/>
       </c>
-      <c r="C139" s="164">
+      <c r="C139" s="257">
         <f>SUM(C133:C137)</f>
         <v/>
       </c>
-      <c r="D139" s="164">
+      <c r="D139" s="257">
         <f>SUM(D133:D137)</f>
         <v/>
       </c>
       <c r="E139" s="164" t="n"/>
-      <c r="F139" s="164">
+      <c r="F139" s="257">
         <f>SUM(F133:F137)</f>
         <v/>
       </c>
-      <c r="G139" s="164" t="inlineStr">
+      <c r="G139" s="257" t="inlineStr">
         <is>
           <t>Sch K items</t>
         </is>
@@ -16263,7 +16517,7 @@
     <row r="141" ht="15" customHeight="1" s="143"/>
     <row r="142" ht="15" customHeight="1" s="143"/>
     <row r="143" ht="15" customHeight="1" s="143">
-      <c r="A143" s="8" t="inlineStr">
+      <c r="A143" s="200" t="inlineStr">
         <is>
           <t>DISTRIBUTIONS (from Balance Sheet — not on P&amp;L)</t>
         </is>
@@ -16277,7 +16531,7 @@
       <c r="J143" s="8" t="n"/>
     </row>
     <row r="144" ht="15" customHeight="1" s="143">
-      <c r="A144" s="67" t="inlineStr">
+      <c r="A144" s="258" t="inlineStr">
         <is>
           <t>Distributions - [SH1 Name] ([%]%)</t>
         </is>
@@ -16307,7 +16561,7 @@
       </c>
     </row>
     <row r="145" ht="15" customHeight="1" s="143">
-      <c r="A145" s="67" t="inlineStr">
+      <c r="A145" s="258" t="inlineStr">
         <is>
           <t>Distributions - [SH2 Name] ([%]%)</t>
         </is>
@@ -16340,37 +16594,37 @@
       </c>
     </row>
     <row r="146" ht="15" customHeight="1" s="143">
-      <c r="A146" s="64" t="inlineStr">
+      <c r="A146" s="242" t="inlineStr">
         <is>
           <t>TOTAL DISTRIBUTIONS</t>
         </is>
       </c>
-      <c r="B146" s="10">
+      <c r="B146" s="250">
         <f>SUM(B144:B145)</f>
         <v/>
       </c>
-      <c r="C146">
+      <c r="C146" s="243">
         <f>SUM(C144:C145)</f>
         <v/>
       </c>
-      <c r="D146" s="32">
+      <c r="D146" s="202">
         <f>SUM(D144:D145)</f>
         <v/>
       </c>
-      <c r="E146" s="32">
+      <c r="E146" s="202">
         <f>SUM(E144:E145)</f>
         <v/>
       </c>
-      <c r="F146" s="32">
+      <c r="F146" s="202">
         <f>SUM(F144:F145)</f>
         <v/>
       </c>
-      <c r="G146" s="64" t="inlineStr">
+      <c r="G146" s="244" t="inlineStr">
         <is>
           <t>Sch K, Ln 16d</t>
         </is>
       </c>
-      <c r="H146" s="32" t="n">
+      <c r="H146" s="202" t="n">
         <v>0</v>
       </c>
       <c r="I146" s="64" t="n"/>
@@ -16379,19 +16633,19 @@
     <row r="147" ht="15" customHeight="1" s="143"/>
     <row r="148" ht="15" customHeight="1" s="143"/>
     <row r="149" ht="15" customHeight="1" s="143">
-      <c r="A149" s="83" t="inlineStr">
+      <c r="A149" s="259" t="inlineStr">
         <is>
           <t>RECONCILIATION — ORDINARY BUSINESS INCOME (Pg 1, Line 21 / Sch K, Line 1)</t>
         </is>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1" s="143">
-      <c r="A150" t="inlineStr">
+      <c r="A150" s="201" t="inlineStr">
         <is>
           <t>Total Income (per WTB, Col D)</t>
         </is>
       </c>
-      <c r="F150" s="10">
+      <c r="F150" s="250">
         <f>F74</f>
         <v/>
       </c>
@@ -16408,12 +16662,12 @@
       </c>
     </row>
     <row r="152" ht="15" customHeight="1" s="143">
-      <c r="A152" s="173" t="inlineStr">
+      <c r="A152" s="201" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="F152" s="38">
+      <c r="F152" s="202">
         <f>F150+F151</f>
         <v/>
       </c>
@@ -16441,14 +16695,14 @@
       </c>
     </row>
     <row r="155" ht="15" customHeight="1" s="143">
-      <c r="A155" s="65" t="inlineStr">
+      <c r="A155" s="242" t="inlineStr">
         <is>
           <t>ORDINARY BUSINESS INCOME (Pg 1, Ln 21 / Sch K, Ln 1)</t>
         </is>
       </c>
       <c r="D155" s="66" t="n"/>
       <c r="E155" s="66" t="n"/>
-      <c r="F155" s="39">
+      <c r="F155" s="245">
         <f>F152+F153+F154</f>
         <v/>
       </c>
@@ -16459,7 +16713,7 @@
     </row>
     <row r="156" ht="15" customHeight="1" s="143"/>
     <row r="157" ht="15" customHeight="1" s="143">
-      <c r="A157" s="162" t="inlineStr">
+      <c r="A157" s="248" t="inlineStr">
         <is>
           <t>M-1 PROOF — Net Income Per Books → Income Per Return</t>
         </is>
@@ -16594,23 +16848,23 @@
       </c>
     </row>
     <row r="170" ht="15" customHeight="1" s="143">
-      <c r="A170" s="173" t="inlineStr">
+      <c r="A170" s="201" t="inlineStr">
         <is>
           <t xml:space="preserve">   Total Line 3</t>
         </is>
       </c>
-      <c r="H170" s="38">
+      <c r="H170" s="202">
         <f>SUM(H160:H169)</f>
         <v/>
       </c>
     </row>
     <row r="171" ht="15" customHeight="1" s="143">
-      <c r="A171" t="inlineStr">
+      <c r="A171" s="201" t="inlineStr">
         <is>
           <t>Line 4: Total (Lines 1 + 3)</t>
         </is>
       </c>
-      <c r="H171" s="10">
+      <c r="H171" s="250">
         <f>H158+H170</f>
         <v/>
       </c>
@@ -16645,12 +16899,12 @@
       </c>
     </row>
     <row r="175" ht="15" customHeight="1" s="143">
-      <c r="A175" s="173" t="inlineStr">
+      <c r="A175" s="201" t="inlineStr">
         <is>
           <t xml:space="preserve">   Total Line 5</t>
         </is>
       </c>
-      <c r="H175" s="38">
+      <c r="H175" s="202">
         <f>SUM(H173:H174)</f>
         <v/>
       </c>
@@ -16685,12 +16939,12 @@
       </c>
     </row>
     <row r="179" ht="15" customHeight="1" s="143">
-      <c r="A179" s="173" t="inlineStr">
+      <c r="A179" s="201" t="inlineStr">
         <is>
           <t xml:space="preserve">   Total Line 6</t>
         </is>
       </c>
-      <c r="H179" s="38">
+      <c r="H179" s="202">
         <f>SUM(H177:H178)</f>
         <v/>
       </c>
@@ -19977,17 +20231,17 @@
     </row>
     <row r="69" ht="15" customHeight="1" s="143"/>
     <row r="70" ht="15" customHeight="1" s="143">
-      <c r="A70" s="173" t="inlineStr">
+      <c r="A70" s="201" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B70" s="173" t="inlineStr">
+      <c r="B70" s="244" t="inlineStr">
         <is>
           <t>Total Sch K Income (Ln 1 through Ln 10 minus Ln 11-12a)</t>
         </is>
       </c>
-      <c r="D70" s="32">
+      <c r="D70" s="202">
         <f>D11+D15+D16+D17+D21+D24-D27-D28</f>
         <v/>
       </c>
@@ -20128,7 +20382,7 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="143">
-      <c r="A4" s="145" t="inlineStr">
+      <c r="A4" s="201" t="inlineStr">
         <is>
           <t>M-1 reconciles book net income → income per return. If gross receipts &gt; $250K AND total assets &gt; $10M at year-end, use Schedule M-3 instead.</t>
         </is>
@@ -20136,7 +20390,7 @@
     </row>
     <row r="5" ht="15" customHeight="1" s="143"/>
     <row r="6" ht="27.75" customHeight="1" s="143">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="260" t="inlineStr">
         <is>
           <t>M-1 Line</t>
         </is>
@@ -21204,7 +21458,7 @@
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="143">
-      <c r="A48" s="145" t="inlineStr">
+      <c r="A48" s="201" t="inlineStr">
         <is>
           <t>If gross receipts &gt; $250K AND total assets &gt; $10M → use Schedule M-3 (separate tab) instead of M-1. Both are included in this workbook.</t>
         </is>
